--- a/course-design-2/outputs/tables/ch4/59_business_time_dimension_analysis.xlsx
+++ b/course-design-2/outputs/tables/ch4/59_business_time_dimension_analysis.xlsx
@@ -893,10 +893,6 @@
       <c r="C5" t="n">
         <v>0</v>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2036,10 +2032,6 @@
       <c r="C5" t="n">
         <v>0</v>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3063,7 +3055,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>主口径岗位数</t>
+          <t>主统计范围岗位数</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -4679,10 +4671,6 @@
       <c r="C5" t="n">
         <v>0</v>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>是</t>
